--- a/clustering/cluster_validation.xlsx
+++ b/clustering/cluster_validation.xlsx
@@ -463,16 +463,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09747525149377322</v>
+        <v>0.09609018111703711</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8393865236829747</v>
+        <v>0.840035148936199</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9112605042016807</v>
+        <v>0.9021368547418966</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9209850728017785</v>
+        <v>0.9198832784971065</v>
       </c>
     </row>
     <row r="3">
@@ -483,16 +483,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1367304741914455</v>
+        <v>0.1290399942836246</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5934293360674014</v>
+        <v>0.6484643434423628</v>
       </c>
       <c r="E3" t="n">
-        <v>0.942376950780312</v>
+        <v>0.9495798319327731</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9628998384397928</v>
+        <v>0.9657479756722036</v>
       </c>
     </row>
     <row r="4">
@@ -503,16 +503,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05582099085246753</v>
+        <v>0.05178444325613706</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9484271188359096</v>
+        <v>0.9549587565162628</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7683553421368547</v>
+        <v>0.7760384153661464</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9850356346935362</v>
+        <v>0.9859828029127449</v>
       </c>
     </row>
     <row r="5">
@@ -523,16 +523,16 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09248522930461288</v>
+        <v>0.08382445885992588</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8997729633012185</v>
+        <v>0.9192681777201058</v>
       </c>
       <c r="E5" t="n">
-        <v>0.876110444177671</v>
+        <v>0.9214405762304921</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9687315901041542</v>
+        <v>0.9730223026416094</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/cluster_validation.xlsx
+++ b/clustering/cluster_validation.xlsx
@@ -463,16 +463,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09609018111703711</v>
+        <v>0.09586869255875365</v>
       </c>
       <c r="D2" t="n">
-        <v>0.840035148936199</v>
+        <v>0.8409215660508893</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9021368547418966</v>
+        <v>0.8981992797118846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9198832784971065</v>
+        <v>0.9196772046293406</v>
       </c>
     </row>
     <row r="3">
@@ -483,16 +483,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1290399942836246</v>
+        <v>0.1258220725611319</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6484643434423628</v>
+        <v>0.6741071699285814</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9495798319327731</v>
+        <v>0.9500600240096039</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9657479756722036</v>
+        <v>0.9656885244735139</v>
       </c>
     </row>
     <row r="4">
@@ -503,16 +503,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05178444325613706</v>
+        <v>0.05201816024869112</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9549587565162628</v>
+        <v>0.9538976899244703</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7760384153661464</v>
+        <v>0.7848739495798319</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9859828029127449</v>
+        <v>0.9859460093035048</v>
       </c>
     </row>
     <row r="5">
@@ -523,16 +523,16 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08382445885992588</v>
+        <v>0.08377156002573236</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9192681777201058</v>
+        <v>0.918571131159624</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9214405762304921</v>
+        <v>0.9231692677070827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9730223026416094</v>
+        <v>0.9727489114831354</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/cluster_validation.xlsx
+++ b/clustering/cluster_validation.xlsx
@@ -463,16 +463,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09586869255875365</v>
+        <v>0.09586869255875356</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8409215660508893</v>
+        <v>0.8409215660508895</v>
       </c>
       <c r="E2" t="n">
         <v>0.8981992797118846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9196772046293406</v>
+        <v>0.9196772046293408</v>
       </c>
     </row>
     <row r="3">
@@ -483,16 +483,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1258220725611319</v>
+        <v>0.1258220725611318</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6741071699285814</v>
+        <v>0.674107169928582</v>
       </c>
       <c r="E3" t="n">
         <v>0.9500600240096039</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9656885244735139</v>
+        <v>0.9656885244735142</v>
       </c>
     </row>
     <row r="4">
@@ -503,16 +503,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05201816024869112</v>
+        <v>0.05201816024869143</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9538976899244703</v>
+        <v>0.9538976899244698</v>
       </c>
       <c r="E4" t="n">
         <v>0.7848739495798319</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9859460093035048</v>
+        <v>0.9859460093035046</v>
       </c>
     </row>
     <row r="5">
@@ -523,10 +523,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08377156002573236</v>
+        <v>0.0837715600257324</v>
       </c>
       <c r="D5" t="n">
-        <v>0.918571131159624</v>
+        <v>0.9185711311596239</v>
       </c>
       <c r="E5" t="n">
         <v>0.9231692677070827</v>

--- a/clustering/cluster_validation.xlsx
+++ b/clustering/cluster_validation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,16 +463,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09586869255875356</v>
+        <v>0.05327941125230271</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8409215660508895</v>
+        <v>0.7100318774882641</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8981992797118846</v>
+        <v>0.9438175270108043</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9196772046293408</v>
+        <v>0.9384814103585983</v>
       </c>
     </row>
     <row r="3">
@@ -483,16 +483,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1258220725611318</v>
+        <v>0.09165709121972587</v>
       </c>
       <c r="D3" t="n">
-        <v>0.674107169928582</v>
+        <v>0.4500485013962341</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9500600240096039</v>
+        <v>0.9519807923169267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9656885244735142</v>
+        <v>0.95575727315251</v>
       </c>
     </row>
     <row r="4">
@@ -503,16 +503,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05201816024869143</v>
+        <v>0.09653073994658849</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9538976899244698</v>
+        <v>0.7998734783190444</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7848739495798319</v>
+        <v>0.9538055222088836</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9859460093035046</v>
+        <v>0.9683529590596233</v>
       </c>
     </row>
     <row r="5">
@@ -523,16 +523,36 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0837715600257324</v>
+        <v>0.09183355276061106</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9185711311596239</v>
+        <v>0.8827560012203413</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9231692677070827</v>
+        <v>0.9598559423769507</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9727489114831354</v>
+        <v>0.9758154712178962</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.09861037359932748</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8632341167734748</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8553661464585834</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.963177652307022</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/cluster_validation.xlsx
+++ b/clustering/cluster_validation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,100 +459,66 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>0.05327941125230271</v>
+        <v>0.3602856351660009</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7100318774882641</v>
+        <v>0.8041139883661723</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9438175270108043</v>
+        <v>0.9033853541416567</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9384814103585983</v>
+        <v>0.9016554207363513</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09165709121972587</v>
+        <v>0.1442876346072846</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4500485013962341</v>
+        <v>0.9546115187804232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9519807923169267</v>
+        <v>0.9375750300120047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.95575727315251</v>
+        <v>0.9783441716158835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
-        <v>2</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DSU</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09653073994658849</v>
+        <v>0.2111387106473778</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7998734783190444</v>
+        <v>0.9366560281188716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9538055222088836</v>
+        <v>0.9357503001200479</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9683529590596233</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.09183355276061106</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.8827560012203413</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9598559423769507</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9758154712178962</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.09861037359932748</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.8632341167734748</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8553661464585834</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.963177652307022</v>
+        <v>0.9721729865840283</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/cluster_validation.xlsx
+++ b/clustering/cluster_validation.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3602856351660009</v>
+        <v>0.3664487834283238</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8041139883661723</v>
+        <v>0.7969364371082429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9033853541416567</v>
+        <v>0.9015606242496997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9016554207363513</v>
+        <v>0.8990421332062494</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1442876346072846</v>
+        <v>0.142867414848957</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9546115187804232</v>
+        <v>0.9555487778975927</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9375750300120047</v>
+        <v>0.946986794717887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9783441716158835</v>
+        <v>0.9790190699252201</v>
       </c>
     </row>
     <row r="4">
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2111387106473778</v>
+        <v>0.2164525854339497</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9366560281188716</v>
+        <v>0.9335398033621432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9357503001200479</v>
+        <v>0.9337334933973589</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9721729865840283</v>
+        <v>0.9716833473958796</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/cluster_validation.xlsx
+++ b/clustering/cluster_validation.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3664487834283238</v>
+        <v>0.3664487786678225</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7969364371082429</v>
+        <v>0.7969364216140036</v>
       </c>
       <c r="E2" t="n">
         <v>0.9015606242496997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8990421332062494</v>
+        <v>0.8990421179851659</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.142867414848957</v>
+        <v>0.1428676437060339</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9555487778975927</v>
+        <v>0.9555486580574073</v>
       </c>
       <c r="E3" t="n">
         <v>0.946986794717887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9790190699252201</v>
+        <v>0.979019018881123</v>
       </c>
     </row>
     <row r="4">
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2164525854339497</v>
+        <v>0.2164526308065631</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9335398033621432</v>
+        <v>0.9335397771999173</v>
       </c>
       <c r="E4" t="n">
         <v>0.9337334933973589</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9716833473958796</v>
+        <v>0.9716833336545638</v>
       </c>
     </row>
   </sheetData>
